--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/58.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/58.xlsx
@@ -426,13 +426,13 @@
         <v>-5.269606225676597</v>
       </c>
       <c r="E2">
-        <v>-10.43593835449406</v>
+        <v>-7.806013489117473</v>
       </c>
       <c r="F2">
-        <v>0.562480371703621</v>
+        <v>-1.076408086569478</v>
       </c>
       <c r="G2">
-        <v>-8.357988792844125</v>
+        <v>-6.609012389899546</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-5.31350110507687</v>
       </c>
       <c r="E3">
-        <v>-10.12658018113406</v>
+        <v>-7.104430596531127</v>
       </c>
       <c r="F3">
-        <v>0.7181455173028984</v>
+        <v>-0.284829308495701</v>
       </c>
       <c r="G3">
-        <v>-8.393271768272834</v>
+        <v>-6.855438691456963</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-5.333746480599109</v>
       </c>
       <c r="E4">
-        <v>-10.69196016099171</v>
+        <v>-8.721526022300173</v>
       </c>
       <c r="F4">
-        <v>0.5558766267685032</v>
+        <v>-0.2070331838617854</v>
       </c>
       <c r="G4">
-        <v>-8.302575523148223</v>
+        <v>-5.498256548817881</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-5.333774654945415</v>
       </c>
       <c r="E5">
-        <v>-10.74049634540592</v>
+        <v>-9.717002349510317</v>
       </c>
       <c r="F5">
-        <v>0.6705293022551773</v>
+        <v>-0.1915418850620318</v>
       </c>
       <c r="G5">
-        <v>-8.06576320075998</v>
+        <v>-6.430884715101971</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-5.317008363007048</v>
       </c>
       <c r="E6">
-        <v>-11.73495376596434</v>
+        <v>-8.980423409792696</v>
       </c>
       <c r="F6">
-        <v>0.3575754109471352</v>
+        <v>-0.1051994939334338</v>
       </c>
       <c r="G6">
-        <v>-7.702545099015687</v>
+        <v>-7.09270710364197</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-5.28807185709575</v>
       </c>
       <c r="E7">
-        <v>-12.48367807297053</v>
+        <v>-10.65090048716416</v>
       </c>
       <c r="F7">
-        <v>1.025357165774734</v>
+        <v>-0.2836439147422949</v>
       </c>
       <c r="G7">
-        <v>-7.928473609491252</v>
+        <v>-7.292448184851608</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-5.252743919415114</v>
       </c>
       <c r="E8">
-        <v>-12.21511239347163</v>
+        <v>-10.30466694995971</v>
       </c>
       <c r="F8">
-        <v>0.4286460206377216</v>
+        <v>0.5567613231546932</v>
       </c>
       <c r="G8">
-        <v>-7.433934458494864</v>
+        <v>-6.187227764540725</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-5.216295302277056</v>
       </c>
       <c r="E9">
-        <v>-12.66068253650834</v>
+        <v>-10.53217748410507</v>
       </c>
       <c r="F9">
-        <v>1.382136662895287</v>
+        <v>-0.1957011177914882</v>
       </c>
       <c r="G9">
-        <v>-6.988613630890146</v>
+        <v>-5.564402694234727</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-5.18712930913917</v>
       </c>
       <c r="E10">
-        <v>-13.69476863310788</v>
+        <v>-11.55755532518786</v>
       </c>
       <c r="F10">
-        <v>1.061638001282547</v>
+        <v>0.3676773514242752</v>
       </c>
       <c r="G10">
-        <v>-7.094337870757014</v>
+        <v>-4.820503829606777</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-5.171297236328788</v>
       </c>
       <c r="E11">
-        <v>-15.7796690092913</v>
+        <v>-12.88851459230824</v>
       </c>
       <c r="F11">
-        <v>1.088912826387124</v>
+        <v>0.1728693609405127</v>
       </c>
       <c r="G11">
-        <v>-7.400072252001395</v>
+        <v>-6.159629410004236</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-5.174197027847423</v>
       </c>
       <c r="E12">
-        <v>-16.2568207300575</v>
+        <v>-13.54270247593031</v>
       </c>
       <c r="F12">
-        <v>1.026543387895543</v>
+        <v>0.6671959518263121</v>
       </c>
       <c r="G12">
-        <v>-5.270418367394718</v>
+        <v>-4.595461248952262</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-5.198071376948568</v>
       </c>
       <c r="E13">
-        <v>-17.28606135946884</v>
+        <v>-13.9893232249368</v>
       </c>
       <c r="F13">
-        <v>0.9984136876312776</v>
+        <v>0.4732436648696414</v>
       </c>
       <c r="G13">
-        <v>-4.919750938115302</v>
+        <v>-2.752733783611228</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-5.246606537550516</v>
       </c>
       <c r="E14">
-        <v>-17.3751273862517</v>
+        <v>-13.52365571425405</v>
       </c>
       <c r="F14">
-        <v>1.168795608508691</v>
+        <v>0.8625382392848803</v>
       </c>
       <c r="G14">
-        <v>-4.060195575960045</v>
+        <v>-3.615609741984643</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-5.322519151514125</v>
       </c>
       <c r="E15">
-        <v>-17.76028315755208</v>
+        <v>-16.21048991248503</v>
       </c>
       <c r="F15">
-        <v>1.283410179094836</v>
+        <v>0.9696279203839947</v>
       </c>
       <c r="G15">
-        <v>-4.630143760835592</v>
+        <v>-2.299400212958346</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-5.427984848881236</v>
       </c>
       <c r="E16">
-        <v>-19.21251043012387</v>
+        <v>-16.21948346186426</v>
       </c>
       <c r="F16">
-        <v>1.465322974219219</v>
+        <v>1.450932575697786</v>
       </c>
       <c r="G16">
-        <v>-3.632921466932273</v>
+        <v>-1.640964045067694</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-5.563213257653476</v>
       </c>
       <c r="E17">
-        <v>-20.07116344366626</v>
+        <v>-17.58098728616638</v>
       </c>
       <c r="F17">
-        <v>1.341824991605452</v>
+        <v>1.523474365895744</v>
       </c>
       <c r="G17">
-        <v>-2.949177237153624</v>
+        <v>-3.157659492597622</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-5.725723545490737</v>
       </c>
       <c r="E18">
-        <v>-20.51929670299131</v>
+        <v>-18.69697989214266</v>
       </c>
       <c r="F18">
-        <v>1.642239057169915</v>
+        <v>0.8394963716086092</v>
       </c>
       <c r="G18">
-        <v>-2.72607385844074</v>
+        <v>-0.4467109589628385</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-5.91354184762806</v>
       </c>
       <c r="E19">
-        <v>-21.39426580838334</v>
+        <v>-19.80910518131638</v>
       </c>
       <c r="F19">
-        <v>1.87554707943359</v>
+        <v>1.006699018394078</v>
       </c>
       <c r="G19">
-        <v>-1.751751209800785</v>
+        <v>-1.252181946153768</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-6.122663358430766</v>
       </c>
       <c r="E20">
-        <v>-22.62988711222024</v>
+        <v>-19.53869641289636</v>
       </c>
       <c r="F20">
-        <v>1.604006588061107</v>
+        <v>1.608975135743098</v>
       </c>
       <c r="G20">
-        <v>-2.119494116075552</v>
+        <v>-0.8698113541669968</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-6.35262575505818</v>
       </c>
       <c r="E21">
-        <v>-23.34259193696943</v>
+        <v>-20.95832320108694</v>
       </c>
       <c r="F21">
-        <v>1.647028677492902</v>
+        <v>1.178207518939299</v>
       </c>
       <c r="G21">
-        <v>-1.159720403830175</v>
+        <v>-0.1379316041112935</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-6.600959438513037</v>
       </c>
       <c r="E22">
-        <v>-24.02024637289924</v>
+        <v>-21.31955051573079</v>
       </c>
       <c r="F22">
-        <v>2.072488115979561</v>
+        <v>1.637195956421672</v>
       </c>
       <c r="G22">
-        <v>-0.376230319865966</v>
+        <v>0.6119193964254884</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-6.864280890880182</v>
       </c>
       <c r="E23">
-        <v>-23.95475558180031</v>
+        <v>-22.97549119153763</v>
       </c>
       <c r="F23">
-        <v>1.631157158055263</v>
+        <v>2.146289024629775</v>
       </c>
       <c r="G23">
-        <v>-0.6147948145669535</v>
+        <v>-0.8043641089423125</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-7.139645395181164</v>
       </c>
       <c r="E24">
-        <v>-24.88633514076223</v>
+        <v>-22.46522726882734</v>
       </c>
       <c r="F24">
-        <v>1.681465567162083</v>
+        <v>1.453223839933929</v>
       </c>
       <c r="G24">
-        <v>0.07007815542814479</v>
+        <v>1.393772150831535</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-7.420832611060659</v>
       </c>
       <c r="E25">
-        <v>-25.3206067411498</v>
+        <v>-22.15738160578591</v>
       </c>
       <c r="F25">
-        <v>1.793990995158367</v>
+        <v>1.409659998220703</v>
       </c>
       <c r="G25">
-        <v>0.1511866711560587</v>
+        <v>0.2913637373970964</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-7.70820863140799</v>
       </c>
       <c r="E26">
-        <v>-25.1088960528172</v>
+        <v>-23.90607448621786</v>
       </c>
       <c r="F26">
-        <v>2.195729304698461</v>
+        <v>1.544397269755654</v>
       </c>
       <c r="G26">
-        <v>0.2641624106692997</v>
+        <v>0.6577777489402878</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-7.998696258503769</v>
       </c>
       <c r="E27">
-        <v>-25.57620287109073</v>
+        <v>-22.84630741352082</v>
       </c>
       <c r="F27">
-        <v>1.572059770804741</v>
+        <v>1.928209708699166</v>
       </c>
       <c r="G27">
-        <v>0.9395526503576028</v>
+        <v>2.610708321576832</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-8.288552326600227</v>
       </c>
       <c r="E28">
-        <v>-25.51159060394929</v>
+        <v>-23.06215712709642</v>
       </c>
       <c r="F28">
-        <v>2.40826352923473</v>
+        <v>2.779503007738551</v>
       </c>
       <c r="G28">
-        <v>1.345236321524228</v>
+        <v>2.462147734251412</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-8.571842265795524</v>
       </c>
       <c r="E29">
-        <v>-25.05964436950978</v>
+        <v>-22.66482881766343</v>
       </c>
       <c r="F29">
-        <v>1.97577953517233</v>
+        <v>1.54252018922091</v>
       </c>
       <c r="G29">
-        <v>0.245984443229976</v>
+        <v>1.354049682632897</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-8.842420669149069</v>
       </c>
       <c r="E30">
-        <v>-24.06136038841488</v>
+        <v>-21.18916216362793</v>
       </c>
       <c r="F30">
-        <v>1.956344379167848</v>
+        <v>2.041117842435544</v>
       </c>
       <c r="G30">
-        <v>0.7086169957823243</v>
+        <v>1.112623962732074</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-9.096425176539602</v>
       </c>
       <c r="E31">
-        <v>-24.49775131463804</v>
+        <v>-22.95007286693258</v>
       </c>
       <c r="F31">
-        <v>2.067196505010478</v>
+        <v>1.368707170561101</v>
       </c>
       <c r="G31">
-        <v>0.2416204185559145</v>
+        <v>0.5581204877368329</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-9.329214032672828</v>
       </c>
       <c r="E32">
-        <v>-24.02412274664981</v>
+        <v>-21.96105867213138</v>
       </c>
       <c r="F32">
-        <v>1.686858238954307</v>
+        <v>1.855595022169761</v>
       </c>
       <c r="G32">
-        <v>-0.2157523358366439</v>
+        <v>1.285032468351537</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-9.535074746031462</v>
       </c>
       <c r="E33">
-        <v>-24.53940421856059</v>
+        <v>-22.58380536071819</v>
       </c>
       <c r="F33">
-        <v>1.986390921602192</v>
+        <v>1.708178759167561</v>
       </c>
       <c r="G33">
-        <v>-0.2107648790662879</v>
+        <v>0.2814708543953706</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-9.706259184482729</v>
       </c>
       <c r="E34">
-        <v>-23.18328022137958</v>
+        <v>-19.57790394085477</v>
       </c>
       <c r="F34">
-        <v>2.267772417719934</v>
+        <v>2.126684881675122</v>
       </c>
       <c r="G34">
-        <v>-0.09063607655345739</v>
+        <v>0.6838929913319083</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-9.838052894724312</v>
       </c>
       <c r="E35">
-        <v>-23.25971633415505</v>
+        <v>-20.29692145837065</v>
       </c>
       <c r="F35">
-        <v>1.843452812779526</v>
+        <v>1.564718778881132</v>
       </c>
       <c r="G35">
-        <v>-0.5170340994248577</v>
+        <v>1.269043075692363</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-9.926175550664482</v>
       </c>
       <c r="E36">
-        <v>-22.75338765535743</v>
+        <v>-20.71406184158721</v>
       </c>
       <c r="F36">
-        <v>2.13555835329391</v>
+        <v>2.220724462710533</v>
       </c>
       <c r="G36">
-        <v>-0.711092104893537</v>
+        <v>-0.3285672954934721</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-9.970652753116687</v>
       </c>
       <c r="E37">
-        <v>-22.40760696555374</v>
+        <v>-19.70820625195148</v>
       </c>
       <c r="F37">
-        <v>1.959101185884365</v>
+        <v>1.60697545683274</v>
       </c>
       <c r="G37">
-        <v>-2.824008478325486</v>
+        <v>-0.6730102474746217</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-9.971074697203361</v>
       </c>
       <c r="E38">
-        <v>-20.28403794981883</v>
+        <v>-18.66192497484928</v>
       </c>
       <c r="F38">
-        <v>2.641326354747176</v>
+        <v>1.942719392126602</v>
       </c>
       <c r="G38">
-        <v>-1.904347699644321</v>
+        <v>-0.2815473905466293</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-9.927158223076384</v>
       </c>
       <c r="E39">
-        <v>-22.08743932473744</v>
+        <v>-18.12629254074803</v>
       </c>
       <c r="F39">
-        <v>2.784090506415254</v>
+        <v>1.934425777689773</v>
       </c>
       <c r="G39">
-        <v>-2.13356727534401</v>
+        <v>-1.174958396752237</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-9.841904407799706</v>
       </c>
       <c r="E40">
-        <v>-20.3811420179653</v>
+        <v>-18.8458398897228</v>
       </c>
       <c r="F40">
-        <v>2.511938679899504</v>
+        <v>2.392070603244805</v>
       </c>
       <c r="G40">
-        <v>-2.823115986061317</v>
+        <v>-1.490145977309377</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-9.718421775630837</v>
       </c>
       <c r="E41">
-        <v>-20.56249381655048</v>
+        <v>-17.0565582967601</v>
       </c>
       <c r="F41">
-        <v>2.562578435967444</v>
+        <v>2.59160774323115</v>
       </c>
       <c r="G41">
-        <v>-2.793391399954308</v>
+        <v>-0.8643382766058431</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-9.564442269609112</v>
       </c>
       <c r="E42">
-        <v>-19.10860459401787</v>
+        <v>-16.43206814568034</v>
       </c>
       <c r="F42">
-        <v>2.811555856022474</v>
+        <v>2.486998194136017</v>
       </c>
       <c r="G42">
-        <v>-2.177762048528171</v>
+        <v>-1.826438374936866</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-9.385463619121621</v>
       </c>
       <c r="E43">
-        <v>-18.06614534897815</v>
+        <v>-14.07328566151302</v>
       </c>
       <c r="F43">
-        <v>2.742456760750551</v>
+        <v>2.725786695136614</v>
       </c>
       <c r="G43">
-        <v>-2.740396390547716</v>
+        <v>-3.038905521918199</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-9.186458296409468</v>
       </c>
       <c r="E44">
-        <v>-18.65432619546441</v>
+        <v>-14.65834186093399</v>
       </c>
       <c r="F44">
-        <v>2.973634222054226</v>
+        <v>2.282063412153031</v>
       </c>
       <c r="G44">
-        <v>-3.181215382172875</v>
+        <v>-1.933393072888526</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-8.97068930981067</v>
       </c>
       <c r="E45">
-        <v>-17.02416159370923</v>
+        <v>-13.08239667847264</v>
       </c>
       <c r="F45">
-        <v>2.869087628881706</v>
+        <v>2.847844975204315</v>
       </c>
       <c r="G45">
-        <v>-3.701541653404941</v>
+        <v>-2.251481253304215</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-8.746059807420085</v>
       </c>
       <c r="E46">
-        <v>-16.05925246605086</v>
+        <v>-11.68011394573145</v>
       </c>
       <c r="F46">
-        <v>3.145457502212511</v>
+        <v>2.424446514815821</v>
       </c>
       <c r="G46">
-        <v>-3.725986754022804</v>
+        <v>-2.659717714844089</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-8.520050206819491</v>
       </c>
       <c r="E47">
-        <v>-15.14390295793244</v>
+        <v>-13.63434973289755</v>
       </c>
       <c r="F47">
-        <v>3.351490699371609</v>
+        <v>2.515172626240034</v>
       </c>
       <c r="G47">
-        <v>-4.060359637038017</v>
+        <v>-1.426168719343324</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-8.298810795702648</v>
       </c>
       <c r="E48">
-        <v>-14.58011247245148</v>
+        <v>-12.1479098391978</v>
       </c>
       <c r="F48">
-        <v>3.304586880290296</v>
+        <v>3.083634786206778</v>
       </c>
       <c r="G48">
-        <v>-4.375665341571298</v>
+        <v>-3.596719749466919</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-8.086963045912878</v>
       </c>
       <c r="E49">
-        <v>-14.01954173198999</v>
+        <v>-9.643396532989643</v>
       </c>
       <c r="F49">
-        <v>3.209056237929846</v>
+        <v>3.130850071431544</v>
       </c>
       <c r="G49">
-        <v>-5.690326134021537</v>
+        <v>-3.278542976069125</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-7.884680955755833</v>
       </c>
       <c r="E50">
-        <v>-13.33638067166684</v>
+        <v>-9.42691736152697</v>
       </c>
       <c r="F50">
-        <v>3.201475019459424</v>
+        <v>3.734638787658076</v>
       </c>
       <c r="G50">
-        <v>-4.237460289487486</v>
+        <v>-4.280037420442841</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-7.696316663429413</v>
       </c>
       <c r="E51">
-        <v>-12.50038361358483</v>
+        <v>-8.997550098489706</v>
       </c>
       <c r="F51">
-        <v>3.12064624176386</v>
+        <v>3.323450462786846</v>
       </c>
       <c r="G51">
-        <v>-3.520536347299732</v>
+        <v>-3.899284470684876</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-7.522680233522069</v>
       </c>
       <c r="E52">
-        <v>-11.92855961521427</v>
+        <v>-8.568640211327214</v>
       </c>
       <c r="F52">
-        <v>3.538531088719321</v>
+        <v>3.19192228657034</v>
       </c>
       <c r="G52">
-        <v>-5.171594536467362</v>
+        <v>-4.992374214890492</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-7.364308253729056</v>
       </c>
       <c r="E53">
-        <v>-11.58330875686948</v>
+        <v>-7.456410767251313</v>
       </c>
       <c r="F53">
-        <v>3.507591566224759</v>
+        <v>3.844331199136786</v>
       </c>
       <c r="G53">
-        <v>-5.350939544463492</v>
+        <v>-3.915352612661477</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-7.219287859408974</v>
       </c>
       <c r="E54">
-        <v>-10.07134638366251</v>
+        <v>-5.782387894731843</v>
       </c>
       <c r="F54">
-        <v>3.431885412548107</v>
+        <v>2.171431632039546</v>
       </c>
       <c r="G54">
-        <v>-5.075943646787989</v>
+        <v>-5.157147317941127</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.083052842182138</v>
       </c>
       <c r="E55">
-        <v>-8.56590954150059</v>
+        <v>-5.467228746168025</v>
       </c>
       <c r="F55">
-        <v>3.886460308508363</v>
+        <v>2.925090235515369</v>
       </c>
       <c r="G55">
-        <v>-4.277405880752166</v>
+        <v>-4.446375666177332</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-6.953737116211355</v>
       </c>
       <c r="E56">
-        <v>-8.91519979866022</v>
+        <v>-5.25034201204466</v>
       </c>
       <c r="F56">
-        <v>3.365299583976277</v>
+        <v>3.414342247691619</v>
       </c>
       <c r="G56">
-        <v>-6.155485227174657</v>
+        <v>-5.188870167977838</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-6.828882676625605</v>
       </c>
       <c r="E57">
-        <v>-9.096035351208521</v>
+        <v>-6.029090101721708</v>
       </c>
       <c r="F57">
-        <v>3.67435683502155</v>
+        <v>3.129198306830362</v>
       </c>
       <c r="G57">
-        <v>-4.918202201539244</v>
+        <v>-3.770598242345014</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-6.708029124634065</v>
       </c>
       <c r="E58">
-        <v>-7.645383987591398</v>
+        <v>-2.413067378804867</v>
       </c>
       <c r="F58">
-        <v>3.61310900599336</v>
+        <v>2.789443416572145</v>
       </c>
       <c r="G58">
-        <v>-5.562004121274772</v>
+        <v>-4.169998374225303</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.589351899911447</v>
       </c>
       <c r="E59">
-        <v>-6.91769897082484</v>
+        <v>-3.757367530351851</v>
       </c>
       <c r="F59">
-        <v>3.367357248604831</v>
+        <v>3.388881547199173</v>
       </c>
       <c r="G59">
-        <v>-5.847936330407904</v>
+        <v>-4.403883846982523</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-6.471015855486751</v>
       </c>
       <c r="E60">
-        <v>-6.363966226114924</v>
+        <v>-3.954043684978982</v>
       </c>
       <c r="F60">
-        <v>3.584467374674165</v>
+        <v>3.740414165190394</v>
       </c>
       <c r="G60">
-        <v>-5.681453710924798</v>
+        <v>-4.596448896641655</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-6.351034005756235</v>
       </c>
       <c r="E61">
-        <v>-6.389343794453909</v>
+        <v>-3.21765946964369</v>
       </c>
       <c r="F61">
-        <v>3.920272609155834</v>
+        <v>3.066649940979777</v>
       </c>
       <c r="G61">
-        <v>-5.75235106515972</v>
+        <v>-5.123882293771477</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-6.230405604761289</v>
       </c>
       <c r="E62">
-        <v>-5.985888459688534</v>
+        <v>-2.952358819904322</v>
       </c>
       <c r="F62">
-        <v>3.414516204846207</v>
+        <v>3.237063339818497</v>
       </c>
       <c r="G62">
-        <v>-6.122174265903174</v>
+        <v>-5.074434284870645</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-6.110637117076755</v>
       </c>
       <c r="E63">
-        <v>-5.087774323643302</v>
+        <v>-3.411881191358664</v>
       </c>
       <c r="F63">
-        <v>3.175823794464335</v>
+        <v>2.792326135133887</v>
       </c>
       <c r="G63">
-        <v>-5.933143091863564</v>
+        <v>-5.278634546179568</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-5.992356825729328</v>
       </c>
       <c r="E64">
-        <v>-5.925741267918656</v>
+        <v>-2.480102379540411</v>
       </c>
       <c r="F64">
-        <v>3.015748420812553</v>
+        <v>2.51469217314641</v>
       </c>
       <c r="G64">
-        <v>-6.052628774950744</v>
+        <v>-5.838440475214871</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-5.876107730848668</v>
       </c>
       <c r="E65">
-        <v>-5.172493015378799</v>
+        <v>-0.4462016776313776</v>
       </c>
       <c r="F65">
-        <v>3.264634720453275</v>
+        <v>2.802657533381602</v>
       </c>
       <c r="G65">
-        <v>-5.849111007726185</v>
+        <v>-5.888748164164277</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-5.760304604584882</v>
       </c>
       <c r="E66">
-        <v>-5.888499097679575</v>
+        <v>-2.162334829948175</v>
       </c>
       <c r="F66">
-        <v>3.139552899365356</v>
+        <v>2.97234528237547</v>
       </c>
       <c r="G66">
-        <v>-5.666517590386206</v>
+        <v>-4.164738576065513</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-5.647438271634561</v>
       </c>
       <c r="E67">
-        <v>-4.562430582487472</v>
+        <v>-0.7199751022390968</v>
       </c>
       <c r="F67">
-        <v>3.160611655479325</v>
+        <v>2.816820959234668</v>
       </c>
       <c r="G67">
-        <v>-6.238857785778588</v>
+        <v>-5.557229943905781</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-5.53829286021523</v>
       </c>
       <c r="E68">
-        <v>-5.420680561843181</v>
+        <v>-2.217718067061983</v>
       </c>
       <c r="F68">
-        <v>2.800967663879891</v>
+        <v>2.819609243912491</v>
       </c>
       <c r="G68">
-        <v>-5.77084402986875</v>
+        <v>-5.544698958770261</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-5.434614939030316</v>
       </c>
       <c r="E69">
-        <v>-4.864991516361951</v>
+        <v>-1.225561111299462</v>
       </c>
       <c r="F69">
-        <v>3.015296132210624</v>
+        <v>1.985385283575193</v>
       </c>
       <c r="G69">
-        <v>-4.88726028223368</v>
+        <v>-4.23170830809378</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-5.337387799843913</v>
       </c>
       <c r="E70">
-        <v>-4.862011780464904</v>
+        <v>-1.434681512499671</v>
       </c>
       <c r="F70">
-        <v>2.56317486049746</v>
+        <v>2.543837451846508</v>
       </c>
       <c r="G70">
-        <v>-4.842002393264259</v>
+        <v>-3.980419236185265</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.246411242037984</v>
       </c>
       <c r="E71">
-        <v>-3.85590259628475</v>
+        <v>-1.470913833035042</v>
       </c>
       <c r="F71">
-        <v>2.621972378748169</v>
+        <v>2.791991474703156</v>
       </c>
       <c r="G71">
-        <v>-5.26154266307642</v>
+        <v>-4.412628302438442</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-5.163631296753623</v>
       </c>
       <c r="E72">
-        <v>-5.003580934892695</v>
+        <v>-2.033508801377968</v>
       </c>
       <c r="F72">
-        <v>2.387570911512798</v>
+        <v>2.299076421871727</v>
       </c>
       <c r="G72">
-        <v>-4.498632400733048</v>
+        <v>-4.032265818046052</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.090113050407209</v>
       </c>
       <c r="E73">
-        <v>-4.644187652221953</v>
+        <v>-3.059597612879964</v>
       </c>
       <c r="F73">
-        <v>2.082847678718972</v>
+        <v>2.171330571216404</v>
       </c>
       <c r="G73">
-        <v>-4.58808178166507</v>
+        <v>-4.040646057908873</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.029407776255667</v>
       </c>
       <c r="E74">
-        <v>-5.004885135406904</v>
+        <v>-0.6533114363721815</v>
       </c>
       <c r="F74">
-        <v>2.137016279922837</v>
+        <v>1.649848440132031</v>
       </c>
       <c r="G74">
-        <v>-3.474382684844583</v>
+        <v>-4.623988189190074</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.983945351528915</v>
       </c>
       <c r="E75">
-        <v>-4.972660514368322</v>
+        <v>-0.05155875328492898</v>
       </c>
       <c r="F75">
-        <v>2.098367970377824</v>
+        <v>3.038586510107735</v>
       </c>
       <c r="G75">
-        <v>-4.91497347952475</v>
+        <v>-2.807398934791577</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.956130042128159</v>
       </c>
       <c r="E76">
-        <v>-4.595719394917857</v>
+        <v>-1.798417601743769</v>
       </c>
       <c r="F76">
-        <v>2.408190632903283</v>
+        <v>1.891532913572815</v>
       </c>
       <c r="G76">
-        <v>-4.454454033656685</v>
+        <v>-3.370246556212486</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-4.94852239721299</v>
       </c>
       <c r="E77">
-        <v>-4.856532326915623</v>
+        <v>-3.890047290302585</v>
       </c>
       <c r="F77">
-        <v>2.013445400977624</v>
+        <v>2.280454722656794</v>
       </c>
       <c r="G77">
-        <v>-3.373606527089357</v>
+        <v>-2.229536443514649</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.96328766626547</v>
       </c>
       <c r="E78">
-        <v>-6.36267108254873</v>
+        <v>-2.849666614832381</v>
       </c>
       <c r="F78">
-        <v>1.838253978959556</v>
+        <v>1.646307997852466</v>
       </c>
       <c r="G78">
-        <v>-3.779040825417465</v>
+        <v>-1.672401428828734</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-5.005572893538798</v>
       </c>
       <c r="E79">
-        <v>-7.444582393143278</v>
+        <v>-4.693144984718876</v>
       </c>
       <c r="F79">
-        <v>1.500459005976363</v>
+        <v>1.419327045811374</v>
       </c>
       <c r="G79">
-        <v>-3.304294002867647</v>
+        <v>-3.065447323112547</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-5.07857966396425</v>
       </c>
       <c r="E80">
-        <v>-8.201181716448811</v>
+        <v>-5.766538235704997</v>
       </c>
       <c r="F80">
-        <v>1.386169155412115</v>
+        <v>2.04002771093346</v>
       </c>
       <c r="G80">
-        <v>-1.775887875592061</v>
+        <v>-2.652699181928437</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-5.185126031071329</v>
       </c>
       <c r="E81">
-        <v>-8.116843416529958</v>
+        <v>-1.993277838293825</v>
       </c>
       <c r="F81">
-        <v>1.762551138752515</v>
+        <v>1.00190608460148</v>
       </c>
       <c r="G81">
-        <v>-2.974600141796202</v>
+        <v>-2.282698795220773</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-5.325632777523105</v>
       </c>
       <c r="E82">
-        <v>-9.996010690070904</v>
+        <v>-7.971293733449425</v>
       </c>
       <c r="F82">
-        <v>1.650323923021238</v>
+        <v>0.6397595950781896</v>
       </c>
       <c r="G82">
-        <v>-1.8230455918444</v>
+        <v>-1.859293246411586</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-5.501137602045128</v>
       </c>
       <c r="E83">
-        <v>-10.2512309566692</v>
+        <v>-6.820916424332909</v>
       </c>
       <c r="F83">
-        <v>1.408180534039303</v>
+        <v>1.553590491191923</v>
       </c>
       <c r="G83">
-        <v>-1.309941289264673</v>
+        <v>-0.4888779372232626</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-5.711778716827197</v>
       </c>
       <c r="E84">
-        <v>-10.72544822627843</v>
+        <v>-6.838518602800724</v>
       </c>
       <c r="F84">
-        <v>1.336405812056337</v>
+        <v>1.539425408604052</v>
       </c>
       <c r="G84">
-        <v>-1.755071806018943</v>
+        <v>-2.365123080794024</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-5.958274729422348</v>
       </c>
       <c r="E85">
-        <v>-11.03407731532319</v>
+        <v>-8.178566517254506</v>
       </c>
       <c r="F85">
-        <v>1.445473634513337</v>
+        <v>1.270010507987152</v>
       </c>
       <c r="G85">
-        <v>-1.595558501128098</v>
+        <v>0.4655276965508625</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-6.239037782531134</v>
       </c>
       <c r="E86">
-        <v>-12.99143774955458</v>
+        <v>-9.670350010283297</v>
       </c>
       <c r="F86">
-        <v>1.128906404594284</v>
+        <v>0.9318477398771149</v>
       </c>
       <c r="G86">
-        <v>-0.953275786974592</v>
+        <v>-0.01613594104626511</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-6.54992194803681</v>
       </c>
       <c r="E87">
-        <v>-13.15957093251136</v>
+        <v>-10.08031276219769</v>
       </c>
       <c r="F87">
-        <v>1.499178349971635</v>
+        <v>1.131691375802496</v>
       </c>
       <c r="G87">
-        <v>-1.012413243140464</v>
+        <v>-0.9194857673554303</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-6.886539051190362</v>
       </c>
       <c r="E88">
-        <v>-15.28532720119198</v>
+        <v>-13.3328122341488</v>
       </c>
       <c r="F88">
-        <v>0.9375071459730411</v>
+        <v>0.8946755810438899</v>
       </c>
       <c r="G88">
-        <v>-0.4304295375848738</v>
+        <v>0.8544837002074391</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-7.241629140075302</v>
       </c>
       <c r="E89">
-        <v>-15.85890824747752</v>
+        <v>-13.28710181751537</v>
       </c>
       <c r="F89">
-        <v>1.282838605586905</v>
+        <v>0.8146072446240953</v>
       </c>
       <c r="G89">
-        <v>-0.3060056160507302</v>
+        <v>-0.668925126633113</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-7.613222725462815</v>
       </c>
       <c r="E90">
-        <v>-18.97401834650991</v>
+        <v>-17.6820718829656</v>
       </c>
       <c r="F90">
-        <v>0.7287005747493698</v>
+        <v>0.143207180981068</v>
       </c>
       <c r="G90">
-        <v>-0.4530962161175179</v>
+        <v>1.4681935370213</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-7.996149788633855</v>
       </c>
       <c r="E91">
-        <v>-19.75827758905429</v>
+        <v>-17.12115697847952</v>
       </c>
       <c r="F91">
-        <v>0.3544955409435267</v>
+        <v>0.7308460463226205</v>
       </c>
       <c r="G91">
-        <v>-0.7287253895539929</v>
+        <v>0.87846942980698</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-8.384187250992673</v>
       </c>
       <c r="E92">
-        <v>-22.5188715719222</v>
+        <v>-18.52972070466936</v>
       </c>
       <c r="F92">
-        <v>0.4407103634920936</v>
+        <v>0.3585031824382707</v>
       </c>
       <c r="G92">
-        <v>-0.2934910370230081</v>
+        <v>2.269786120328966</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-8.770662666091457</v>
       </c>
       <c r="E93">
-        <v>-21.78245112879485</v>
+        <v>-21.05131994330846</v>
       </c>
       <c r="F93">
-        <v>0.4632916588924081</v>
+        <v>-0.3867002749571786</v>
       </c>
       <c r="G93">
-        <v>-0.1357791227682978</v>
+        <v>-0.2383140152793857</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-9.144268837144871</v>
       </c>
       <c r="E94">
-        <v>-25.54968865577582</v>
+        <v>-23.53051002286572</v>
       </c>
       <c r="F94">
-        <v>0.4759159781110726</v>
+        <v>0.6477665943936497</v>
       </c>
       <c r="G94">
-        <v>-0.7156825338552002</v>
+        <v>-0.6824765716736196</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-9.502336914130584</v>
       </c>
       <c r="E95">
-        <v>-25.99774945951675</v>
+        <v>-24.86163231505039</v>
       </c>
       <c r="F95">
-        <v>-0.1037117460780059</v>
+        <v>-0.670809584932339</v>
       </c>
       <c r="G95">
-        <v>-0.5441862078292626</v>
+        <v>0.1174294637524915</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-9.837047848555974</v>
       </c>
       <c r="E96">
-        <v>-29.32338378669173</v>
+        <v>-27.5128908214771</v>
       </c>
       <c r="F96">
-        <v>-0.1443199728980432</v>
+        <v>-0.3790287644398523</v>
       </c>
       <c r="G96">
-        <v>0.1812393794190129</v>
+        <v>-0.1768862664650212</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-10.14168688580251</v>
       </c>
       <c r="E97">
-        <v>-31.67523996986432</v>
+        <v>-29.80123515669212</v>
       </c>
       <c r="F97">
-        <v>-0.5117779542080844</v>
+        <v>-0.3462668336591319</v>
       </c>
       <c r="G97">
-        <v>-0.9228719880047773</v>
+        <v>-0.8811250061039622</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-10.40371836113308</v>
       </c>
       <c r="E98">
-        <v>-32.80576444893121</v>
+        <v>-31.68730382462075</v>
       </c>
       <c r="F98">
-        <v>-0.7224582924968882</v>
+        <v>-0.425531653698211</v>
       </c>
       <c r="G98">
-        <v>-1.427901204326711</v>
+        <v>-0.9468183429456049</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-10.61667433113386</v>
       </c>
       <c r="E99">
-        <v>-36.09634612304981</v>
+        <v>-33.34905226834243</v>
       </c>
       <c r="F99">
-        <v>-1.097745174130787</v>
+        <v>-0.2856104589565409</v>
       </c>
       <c r="G99">
-        <v>-1.252254133028076</v>
+        <v>1.150971599097304</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-10.76821287956945</v>
       </c>
       <c r="E100">
-        <v>-38.19062044042911</v>
+        <v>-36.51566243802706</v>
       </c>
       <c r="F100">
-        <v>-1.172048073427097</v>
+        <v>-0.8699441383609233</v>
       </c>
       <c r="G100">
-        <v>-1.310092225456408</v>
+        <v>-1.918132111415549</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-10.85942616347526</v>
       </c>
       <c r="E101">
-        <v>-40.9294166136611</v>
+        <v>-40.8230291737989</v>
       </c>
       <c r="F101">
-        <v>-1.017637076075658</v>
+        <v>-0.7057128454492961</v>
       </c>
       <c r="G101">
-        <v>-2.17505175952007</v>
+        <v>-2.490255746185007</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-10.87172360151095</v>
       </c>
       <c r="E102">
-        <v>-43.47963354379167</v>
+        <v>-42.02174794294729</v>
       </c>
       <c r="F102">
-        <v>-0.9436083663896749</v>
+        <v>-1.466859061879025</v>
       </c>
       <c r="G102">
-        <v>-2.602043683493729</v>
+        <v>-1.857344200805276</v>
       </c>
     </row>
   </sheetData>
